--- a/ideas_ressources_files/plant_port_checklist.xlsx
+++ b/ideas_ressources_files/plant_port_checklist.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\rogue_garden\ideas_ressources_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_zombie_rpg\ideas_ressources_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4236A5C9-F3BF-463E-82F4-E1213358E3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F0348A-D41A-445A-A669-5E0AE8230374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="956">
   <si>
     <t>Origin Name</t>
   </si>
@@ -2655,9 +2655,6 @@
     <t>Physalux</t>
   </si>
   <si>
-    <t>Acesparagus</t>
-  </si>
-  <si>
     <t>Lime-bomb</t>
   </si>
   <si>
@@ -2899,6 +2896,12 @@
   </si>
   <si>
     <t>Shadow Repeater</t>
+  </si>
+  <si>
+    <t>Aceparagus</t>
+  </si>
+  <si>
+    <t>Squirty-shroom</t>
   </si>
 </sst>
 </file>
@@ -2957,7 +2960,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2992,6 +2995,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3325,7 +3334,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -3339,7 +3348,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="7" t="b">
         <v>0</v>
@@ -3356,7 +3365,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="7" t="b">
         <v>1</v>
@@ -3373,7 +3382,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="7" t="b">
         <v>1</v>
@@ -3390,7 +3399,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="7" t="b">
         <v>1</v>
@@ -3407,7 +3416,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="7" t="b">
         <v>1</v>
@@ -3424,7 +3433,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="7" t="b">
         <v>1</v>
@@ -3441,7 +3450,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="7" t="b">
         <v>1</v>
@@ -3458,7 +3467,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="7" t="b">
         <v>1</v>
@@ -3475,7 +3484,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="7" t="b">
         <v>0</v>
@@ -3492,7 +3501,7 @@
         <v>40</v>
       </c>
       <c r="C11" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="7" t="b">
         <v>1</v>
@@ -3509,7 +3518,7 @@
         <v>40</v>
       </c>
       <c r="C12" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="7" t="b">
         <v>1</v>
@@ -3526,7 +3535,7 @@
         <v>40</v>
       </c>
       <c r="C13" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="7" t="b">
         <v>1</v>
@@ -3543,7 +3552,7 @@
         <v>40</v>
       </c>
       <c r="C14" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="7" t="b">
         <v>1</v>
@@ -3560,7 +3569,7 @@
         <v>40</v>
       </c>
       <c r="C15" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="7" t="b">
         <v>1</v>
@@ -3577,7 +3586,7 @@
         <v>40</v>
       </c>
       <c r="C16" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="7" t="b">
         <v>1</v>
@@ -3594,7 +3603,7 @@
         <v>40</v>
       </c>
       <c r="C17" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="7" t="b">
         <v>1</v>
@@ -3985,7 +3994,7 @@
         <v>22</v>
       </c>
       <c r="C40" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="7" t="b">
         <v>1</v>
@@ -4002,7 +4011,7 @@
         <v>22</v>
       </c>
       <c r="C41" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="7" t="b">
         <v>1</v>
@@ -4019,7 +4028,7 @@
         <v>22</v>
       </c>
       <c r="C42" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="7" t="b">
         <v>0</v>
@@ -4036,7 +4045,7 @@
         <v>22</v>
       </c>
       <c r="C43" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="7" t="b">
         <v>1</v>
@@ -4053,7 +4062,7 @@
         <v>22</v>
       </c>
       <c r="C44" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="7" t="b">
         <v>1</v>
@@ -4070,7 +4079,7 @@
         <v>22</v>
       </c>
       <c r="C45" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="7" t="b">
         <v>1</v>
@@ -4087,7 +4096,7 @@
         <v>22</v>
       </c>
       <c r="C46" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="7" t="b">
         <v>1</v>
@@ -4104,7 +4113,7 @@
         <v>22</v>
       </c>
       <c r="C47" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" s="7" t="b">
         <v>1</v>
@@ -4189,7 +4198,7 @@
         <v>31</v>
       </c>
       <c r="C52" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="7" t="b">
         <v>1</v>
@@ -4206,7 +4215,7 @@
         <v>31</v>
       </c>
       <c r="C53" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="7" t="b">
         <v>1</v>
@@ -4223,7 +4232,7 @@
         <v>31</v>
       </c>
       <c r="C54" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="7" t="b">
         <v>1</v>
@@ -4240,7 +4249,7 @@
         <v>31</v>
       </c>
       <c r="C55" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="7" t="b">
         <v>1</v>
@@ -4257,7 +4266,7 @@
         <v>31</v>
       </c>
       <c r="C56" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="7" t="b">
         <v>1</v>
@@ -4274,7 +4283,7 @@
         <v>31</v>
       </c>
       <c r="C57" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="7" t="b">
         <v>1</v>
@@ -4291,7 +4300,7 @@
         <v>31</v>
       </c>
       <c r="C58" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="7" t="b">
         <v>1</v>
@@ -4308,7 +4317,7 @@
         <v>31</v>
       </c>
       <c r="C59" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="7" t="b">
         <v>1</v>
@@ -4325,7 +4334,7 @@
         <v>49</v>
       </c>
       <c r="C60" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="7" t="b">
         <v>1</v>
@@ -4342,7 +4351,7 @@
         <v>49</v>
       </c>
       <c r="C61" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" s="7" t="b">
         <v>1</v>
@@ -4359,7 +4368,7 @@
         <v>49</v>
       </c>
       <c r="C62" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" s="7" t="b">
         <v>1</v>
@@ -4376,7 +4385,7 @@
         <v>49</v>
       </c>
       <c r="C63" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" s="7" t="b">
         <v>1</v>
@@ -4393,7 +4402,7 @@
         <v>49</v>
       </c>
       <c r="C64" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" s="7" t="b">
         <v>1</v>
@@ -4427,7 +4436,7 @@
         <v>49</v>
       </c>
       <c r="C66" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" s="7" t="b">
         <v>1</v>
@@ -4444,7 +4453,7 @@
         <v>49</v>
       </c>
       <c r="C67" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="7" t="b">
         <v>1</v>
@@ -4461,7 +4470,7 @@
         <v>59</v>
       </c>
       <c r="C68" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" s="7" t="b">
         <v>1</v>
@@ -4478,7 +4487,7 @@
         <v>59</v>
       </c>
       <c r="C69" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" s="7" t="b">
         <v>1</v>
@@ -4495,7 +4504,7 @@
         <v>59</v>
       </c>
       <c r="C70" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" s="7" t="b">
         <v>1</v>
@@ -4512,7 +4521,7 @@
         <v>59</v>
       </c>
       <c r="C71" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" s="7" t="b">
         <v>1</v>
@@ -4529,7 +4538,7 @@
         <v>59</v>
       </c>
       <c r="C72" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>87</v>
@@ -4549,7 +4558,7 @@
         <v>59</v>
       </c>
       <c r="C73" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" s="7" t="b">
         <v>1</v>
@@ -4566,7 +4575,7 @@
         <v>59</v>
       </c>
       <c r="C74" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" s="7" t="b">
         <v>1</v>
@@ -4583,7 +4592,7 @@
         <v>59</v>
       </c>
       <c r="C75" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" s="7" t="b">
         <v>1</v>
@@ -4602,873 +4611,880 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02DA624A-A8AE-417D-8E03-5309B0ED71C8}">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.109375" style="8" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="16.77734375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" style="8" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="16.77734375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="7.109375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" style="8" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="B2" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="B3" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="B4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="B5" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="B6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="B7" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="B8" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="B9" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="B10" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="B11" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="B12" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="B13" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>942</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>806</v>
-      </c>
-      <c r="C2" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>813</v>
-      </c>
-      <c r="C3" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>808</v>
-      </c>
-      <c r="C4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>809</v>
-      </c>
-      <c r="C5" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="B14" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>943</v>
+      </c>
+      <c r="B15" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="B16" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>951</v>
+      </c>
+      <c r="B17" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="C6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>799</v>
-      </c>
-      <c r="E7" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>805</v>
-      </c>
-      <c r="E8" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>801</v>
-      </c>
-      <c r="E9" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>816</v>
-      </c>
-      <c r="E10" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>817</v>
-      </c>
-      <c r="E11" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>818</v>
-      </c>
-      <c r="E12" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>864</v>
-      </c>
-      <c r="E13" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C15" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C16" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>954</v>
+      <c r="B18" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C19" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="7" t="b">
+      <c r="A19" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="B19" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C20" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="7" t="b">
+      <c r="B20" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="7" t="b">
+      <c r="B21" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C22" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" s="7" t="b">
+      <c r="B22" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" s="7" t="b">
+      <c r="B23" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E24" s="7" t="b">
+      <c r="B24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="7" t="b">
+      <c r="B25" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="7" t="b">
+      <c r="B26" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C27" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="7" t="b">
+      <c r="B27" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C28" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="7" t="b">
+      <c r="B28" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C29" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="7" t="b">
+      <c r="B29" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C30" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" s="7" t="b">
+      <c r="B30" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C31" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31" s="7" t="b">
+      <c r="B31" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C32" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C33" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C34" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E34" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C35" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C36" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C37" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C38" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C39" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C40" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C41" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E41" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C42" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C43" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E43" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C44" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E44" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C45" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C46" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C47" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C48" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E48" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C49" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E49" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C50" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E50" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C51" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E51" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C52" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E52" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C53" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E53" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C54" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E54" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C55" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E55" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C56" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E56" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C57" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E57" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C58" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E58" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C59" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E59" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C60" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E60" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C61" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E61" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C62" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E62" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C63" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E63" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C64" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E64" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C65" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E65" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C66" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E66" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C67" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E67" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C68" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E68" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C69" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E69" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C70" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E70" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C71" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E71" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="C72" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E72" s="7" t="b">
+      <c r="B32" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D41" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F45" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F49" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D52" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D55" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D56" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D57" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D58" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F58" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D59" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F59" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D60" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F60" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D61" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D62" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D63" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D64" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F64" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D65" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F65" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D66" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F66" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D67" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D68" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F68" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D69" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F69" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D70" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F70" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D71" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D72" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="7" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F13">
-    <sortCondition ref="B2:B13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:G13">
+    <sortCondition ref="C2:C13"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5510,7 +5526,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -5592,7 +5608,7 @@
         <v>97</v>
       </c>
       <c r="C6" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="7" t="b">
         <v>1</v>
@@ -5711,7 +5727,7 @@
         <v>97</v>
       </c>
       <c r="C13" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="7" t="b">
         <v>0</v>
@@ -5798,7 +5814,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -5812,7 +5828,7 @@
         <v>112</v>
       </c>
       <c r="C2" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="7" t="b">
         <v>0</v>
@@ -5829,7 +5845,7 @@
         <v>113</v>
       </c>
       <c r="C3" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="7" t="b">
         <v>1</v>
@@ -5846,7 +5862,7 @@
         <v>113</v>
       </c>
       <c r="C4" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="7" t="b">
         <v>1</v>
@@ -5863,7 +5879,7 @@
         <v>112</v>
       </c>
       <c r="C5" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="7" t="b">
         <v>0</v>
@@ -5931,7 +5947,7 @@
         <v>113</v>
       </c>
       <c r="C9" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="7" t="b">
         <v>1</v>
@@ -6086,7 +6102,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A72B5E-30F7-44EA-9A7D-62AB51A3920C}">
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:I170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" style="5" customWidth="1"/>
@@ -6120,7 +6136,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -6134,7 +6150,7 @@
         <v>126</v>
       </c>
       <c r="C2" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="7" t="b">
         <v>1</v>
@@ -6151,7 +6167,7 @@
         <v>126</v>
       </c>
       <c r="C3" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="7" t="b">
         <v>1</v>
@@ -6185,7 +6201,7 @@
         <v>175</v>
       </c>
       <c r="C5" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="7" t="b">
         <v>1</v>
@@ -6202,7 +6218,7 @@
         <v>175</v>
       </c>
       <c r="C6" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="7" t="b">
         <v>1</v>
@@ -6219,7 +6235,7 @@
         <v>175</v>
       </c>
       <c r="C7" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="7" t="b">
         <v>1</v>
@@ -6236,7 +6252,7 @@
         <v>155</v>
       </c>
       <c r="C8" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="7" t="b">
         <v>1</v>
@@ -6270,7 +6286,7 @@
         <v>154</v>
       </c>
       <c r="C10" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="7" t="b">
         <v>0</v>
@@ -6287,7 +6303,7 @@
         <v>154</v>
       </c>
       <c r="C11" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="7" t="b">
         <v>1</v>
@@ -6304,7 +6320,7 @@
         <v>154</v>
       </c>
       <c r="C12" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="7" t="b">
         <v>1</v>
@@ -6321,7 +6337,7 @@
         <v>154</v>
       </c>
       <c r="C13" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="7" t="b">
         <v>1</v>
@@ -6355,7 +6371,7 @@
         <v>145</v>
       </c>
       <c r="C15" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="7" t="b">
         <v>1</v>
@@ -6372,7 +6388,7 @@
         <v>145</v>
       </c>
       <c r="C16" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="7" t="b">
         <v>0</v>
@@ -6389,7 +6405,7 @@
         <v>145</v>
       </c>
       <c r="C17" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="7" t="b">
         <v>1</v>
@@ -6406,7 +6422,7 @@
         <v>145</v>
       </c>
       <c r="C18" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="7" t="b">
         <v>1</v>
@@ -6440,7 +6456,7 @@
         <v>205</v>
       </c>
       <c r="C20" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="7" t="b">
         <v>1</v>
@@ -6457,7 +6473,7 @@
         <v>205</v>
       </c>
       <c r="C21" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="7" t="b">
         <v>1</v>
@@ -6474,7 +6490,7 @@
         <v>205</v>
       </c>
       <c r="C22" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="7" t="b">
         <v>1</v>
@@ -6491,7 +6507,7 @@
         <v>205</v>
       </c>
       <c r="C23" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="7" t="b">
         <v>1</v>
@@ -6508,7 +6524,7 @@
         <v>205</v>
       </c>
       <c r="C24" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="7" t="b">
         <v>1</v>
@@ -6542,7 +6558,7 @@
         <v>205</v>
       </c>
       <c r="C26" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="7" t="b">
         <v>1</v>
@@ -6559,7 +6575,7 @@
         <v>205</v>
       </c>
       <c r="C27" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="7" t="b">
         <v>1</v>
@@ -6610,7 +6626,7 @@
         <v>205</v>
       </c>
       <c r="C30" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="7" t="b">
         <v>1</v>
@@ -6644,7 +6660,7 @@
         <v>166</v>
       </c>
       <c r="C32" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="7" t="b">
         <v>1</v>
@@ -6661,7 +6677,7 @@
         <v>166</v>
       </c>
       <c r="C33" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="7" t="b">
         <v>1</v>
@@ -6678,7 +6694,7 @@
         <v>166</v>
       </c>
       <c r="C34" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="7" t="b">
         <v>1</v>
@@ -6695,7 +6711,7 @@
         <v>166</v>
       </c>
       <c r="C35" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="7" t="b">
         <v>1</v>
@@ -6712,7 +6728,7 @@
         <v>146</v>
       </c>
       <c r="C36" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="7" t="b">
         <v>1</v>
@@ -6729,7 +6745,7 @@
         <v>146</v>
       </c>
       <c r="C37" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" s="7" t="b">
         <v>1</v>
@@ -6746,7 +6762,7 @@
         <v>146</v>
       </c>
       <c r="C38" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="7" t="b">
         <v>1</v>
@@ -6780,7 +6796,7 @@
         <v>146</v>
       </c>
       <c r="C40" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="7" t="b">
         <v>1</v>
@@ -6797,7 +6813,7 @@
         <v>176</v>
       </c>
       <c r="C41" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="7" t="b">
         <v>1</v>
@@ -6814,7 +6830,7 @@
         <v>176</v>
       </c>
       <c r="C42" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="7" t="b">
         <v>1</v>
@@ -6831,7 +6847,7 @@
         <v>176</v>
       </c>
       <c r="C43" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="7" t="b">
         <v>1</v>
@@ -6848,7 +6864,7 @@
         <v>176</v>
       </c>
       <c r="C44" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="7" t="b">
         <v>1</v>
@@ -6865,7 +6881,7 @@
         <v>176</v>
       </c>
       <c r="C45" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="7" t="b">
         <v>1</v>
@@ -6882,7 +6898,7 @@
         <v>165</v>
       </c>
       <c r="C46" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="7" t="b">
         <v>1</v>
@@ -6916,7 +6932,7 @@
         <v>165</v>
       </c>
       <c r="C48" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="7" t="b">
         <v>1</v>
@@ -6950,7 +6966,7 @@
         <v>165</v>
       </c>
       <c r="C50" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="7" t="b">
         <v>1</v>
@@ -6987,7 +7003,7 @@
         <v>60</v>
       </c>
       <c r="C52" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="7" t="b">
         <v>0</v>
@@ -7015,7 +7031,7 @@
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>60</v>
@@ -7038,7 +7054,7 @@
         <v>133</v>
       </c>
       <c r="C55" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="7" t="b">
         <v>1</v>
@@ -7055,7 +7071,7 @@
         <v>133</v>
       </c>
       <c r="C56" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="7" t="b">
         <v>1</v>
@@ -7072,7 +7088,7 @@
         <v>133</v>
       </c>
       <c r="C57" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="7" t="b">
         <v>1</v>
@@ -7344,7 +7360,7 @@
         <v>97</v>
       </c>
       <c r="C73" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" s="7" t="b">
         <v>1</v>
@@ -7361,7 +7377,7 @@
         <v>97</v>
       </c>
       <c r="C74" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" s="7" t="b">
         <v>1</v>
@@ -7378,7 +7394,7 @@
         <v>97</v>
       </c>
       <c r="C75" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" s="7" t="b">
         <v>1</v>
@@ -7395,7 +7411,7 @@
         <v>97</v>
       </c>
       <c r="C76" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" s="7" t="b">
         <v>1</v>
@@ -7429,7 +7445,7 @@
         <v>97</v>
       </c>
       <c r="C78" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" s="7" t="b">
         <v>1</v>
@@ -7446,7 +7462,7 @@
         <v>97</v>
       </c>
       <c r="C79" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" s="7" t="b">
         <v>1</v>
@@ -7483,7 +7499,7 @@
         <v>97</v>
       </c>
       <c r="C81" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" s="7" t="b">
         <v>1</v>
@@ -7520,7 +7536,7 @@
         <v>97</v>
       </c>
       <c r="C83" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" s="7" t="b">
         <v>1</v>
@@ -7571,7 +7587,7 @@
         <v>97</v>
       </c>
       <c r="C86" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="7" t="b">
         <v>1</v>
@@ -7588,7 +7604,7 @@
         <v>97</v>
       </c>
       <c r="C87" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" s="7" t="b">
         <v>1</v>
@@ -7605,7 +7621,7 @@
         <v>97</v>
       </c>
       <c r="C88" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" s="7" t="b">
         <v>1</v>
@@ -7622,7 +7638,7 @@
         <v>221</v>
       </c>
       <c r="C89" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" s="7" t="b">
         <v>1</v>
@@ -7750,7 +7766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>224</v>
       </c>
@@ -7767,7 +7783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>253</v>
       </c>
@@ -7783,8 +7799,9 @@
       <c r="G98" s="7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I98" s="11"/>
+    </row>
+    <row r="99" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>227</v>
       </c>
@@ -7795,13 +7812,13 @@
         <v>0</v>
       </c>
       <c r="E99" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" s="7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>259</v>
       </c>
@@ -7818,7 +7835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>280</v>
       </c>
@@ -7835,7 +7852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>270</v>
       </c>
@@ -7852,7 +7869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>288</v>
       </c>
@@ -7869,7 +7886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>278</v>
       </c>
@@ -7886,7 +7903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>269</v>
       </c>
@@ -7903,8 +7920,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="10" t="s">
+    <row r="106" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="12" t="s">
         <v>279</v>
       </c>
       <c r="B106" s="6" t="s">
@@ -7920,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>300</v>
       </c>
@@ -7937,7 +7954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>287</v>
       </c>
@@ -7954,7 +7971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>222</v>
       </c>
@@ -7962,7 +7979,7 @@
         <v>221</v>
       </c>
       <c r="C109" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" s="7" t="b">
         <v>1</v>
@@ -7974,7 +7991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>242</v>
       </c>
@@ -7982,7 +7999,7 @@
         <v>221</v>
       </c>
       <c r="C110" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110" s="7" t="b">
         <v>1</v>
@@ -7991,7 +8008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>235</v>
       </c>
@@ -8008,7 +8025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>257</v>
       </c>
@@ -8067,7 +8084,7 @@
         <v>221</v>
       </c>
       <c r="C115" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115" s="7" t="b">
         <v>1</v>
@@ -8084,7 +8101,7 @@
         <v>221</v>
       </c>
       <c r="C116" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" s="7" t="b">
         <v>1</v>
@@ -8135,7 +8152,7 @@
         <v>221</v>
       </c>
       <c r="C119" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" s="7" t="b">
         <v>1</v>
@@ -8271,7 +8288,7 @@
         <v>221</v>
       </c>
       <c r="C127" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127" s="7" t="b">
         <v>1</v>
@@ -8288,7 +8305,7 @@
         <v>221</v>
       </c>
       <c r="C128" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" s="7" t="b">
         <v>1</v>
@@ -8305,7 +8322,7 @@
         <v>221</v>
       </c>
       <c r="C129" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" s="7" t="b">
         <v>1</v>
@@ -8339,7 +8356,7 @@
         <v>221</v>
       </c>
       <c r="C131" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" s="7" t="b">
         <v>0</v>
@@ -8356,7 +8373,7 @@
         <v>221</v>
       </c>
       <c r="C132" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" s="7" t="b">
         <v>1</v>
@@ -8475,7 +8492,7 @@
         <v>221</v>
       </c>
       <c r="C139" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" s="7" t="b">
         <v>1</v>
@@ -8526,7 +8543,7 @@
         <v>221</v>
       </c>
       <c r="C142" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142" s="7" t="b">
         <v>1</v>
@@ -8543,7 +8560,7 @@
         <v>221</v>
       </c>
       <c r="C143" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" s="7" t="b">
         <v>0</v>
@@ -8560,7 +8577,7 @@
         <v>221</v>
       </c>
       <c r="C144" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" s="7" t="b">
         <v>1</v>
@@ -8628,7 +8645,7 @@
         <v>221</v>
       </c>
       <c r="C148" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" s="7" t="b">
         <v>1</v>
@@ -8645,7 +8662,7 @@
         <v>221</v>
       </c>
       <c r="C149" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" s="7" t="b">
         <v>1</v>
@@ -8662,7 +8679,7 @@
         <v>221</v>
       </c>
       <c r="C150" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" s="7" t="b">
         <v>1</v>
@@ -8679,7 +8696,7 @@
         <v>221</v>
       </c>
       <c r="C151" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" s="7" t="b">
         <v>1</v>
@@ -8713,7 +8730,7 @@
         <v>221</v>
       </c>
       <c r="C153" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" s="7" t="b">
         <v>0</v>
@@ -8928,7 +8945,7 @@
     </row>
     <row r="166" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>221</v>
@@ -8945,7 +8962,7 @@
     </row>
     <row r="167" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="5" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>221</v>
@@ -8957,7 +8974,7 @@
         <v>1</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G167" s="7" t="b">
         <v>0</v>
@@ -8988,7 +9005,7 @@
         <v>134</v>
       </c>
       <c r="C169" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E169" s="7" t="b">
         <v>1</v>
@@ -9005,7 +9022,7 @@
         <v>134</v>
       </c>
       <c r="C170" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E170" s="7" t="b">
         <v>1</v>
@@ -9058,7 +9075,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -10152,7 +10169,7 @@
         <v>361</v>
       </c>
       <c r="C65" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65" s="7" t="b">
         <v>1</v>
@@ -10237,7 +10254,7 @@
         <v>361</v>
       </c>
       <c r="C70" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" s="7" t="b">
         <v>1</v>
@@ -10705,7 +10722,7 @@
         <v>361</v>
       </c>
       <c r="C97" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" s="7" t="b">
         <v>0</v>
@@ -10827,7 +10844,7 @@
         <v>361</v>
       </c>
       <c r="C104" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" s="7" t="b">
         <v>1</v>
@@ -11142,13 +11159,16 @@
         <v>324</v>
       </c>
       <c r="C122" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>954</v>
       </c>
       <c r="E122" s="7" t="b">
         <v>1</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>873</v>
+        <v>954</v>
       </c>
       <c r="G122" s="7" t="b">
         <v>0</v>
@@ -11578,7 +11598,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -11606,10 +11626,10 @@
         <v>769</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C3" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="7" t="b">
         <v>0</v>
@@ -11711,7 +11731,7 @@
         <v>782</v>
       </c>
       <c r="C9" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="7" t="b">
         <v>0</v>
@@ -11722,7 +11742,7 @@
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>823</v>
@@ -11779,7 +11799,7 @@
         <v>776</v>
       </c>
       <c r="C13" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="7" t="b">
         <v>1</v>
@@ -11841,7 +11861,7 @@
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>841</v>
@@ -11892,7 +11912,7 @@
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>841</v>
@@ -11932,7 +11952,7 @@
         <v>788</v>
       </c>
       <c r="C22" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="7" t="b">
         <v>0</v>
@@ -11977,7 +11997,7 @@
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>823</v>
@@ -12147,7 +12167,7 @@
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>820</v>
@@ -12215,7 +12235,7 @@
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>841</v>
@@ -12300,7 +12320,7 @@
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>823</v>
@@ -12317,7 +12337,7 @@
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>841</v>
@@ -12714,7 +12734,7 @@
         <v>556</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C68" s="7" t="b">
         <v>0</v>
@@ -12728,10 +12748,10 @@
     </row>
     <row r="69" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C69" s="7" t="b">
         <v>0</v>
@@ -12745,10 +12765,10 @@
     </row>
     <row r="70" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C70" s="7" t="b">
         <v>0</v>
@@ -12762,10 +12782,10 @@
     </row>
     <row r="71" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C71" s="7" t="b">
         <v>0</v>
@@ -12779,10 +12799,10 @@
     </row>
     <row r="72" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C72" s="7" t="b">
         <v>0</v>
@@ -12796,10 +12816,10 @@
     </row>
     <row r="73" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C73" s="7" t="b">
         <v>0</v>
@@ -12813,10 +12833,10 @@
     </row>
     <row r="74" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C74" s="7" t="b">
         <v>0</v>
@@ -12830,10 +12850,10 @@
     </row>
     <row r="75" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C75" s="7" t="b">
         <v>0</v>
@@ -12847,10 +12867,10 @@
     </row>
     <row r="76" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C76" s="7" t="b">
         <v>0</v>
@@ -12859,7 +12879,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G76" s="7" t="b">
         <v>0</v>
@@ -12867,10 +12887,10 @@
     </row>
     <row r="77" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C77" s="7" t="b">
         <v>0</v>
@@ -12884,10 +12904,10 @@
     </row>
     <row r="78" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C78" s="7" t="b">
         <v>0</v>
@@ -12901,10 +12921,10 @@
     </row>
     <row r="79" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C79" s="7" t="b">
         <v>0</v>
@@ -12918,10 +12938,10 @@
     </row>
     <row r="80" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C80" s="7" t="b">
         <v>0</v>
@@ -12935,10 +12955,10 @@
     </row>
     <row r="81" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C81" s="7" t="b">
         <v>0</v>
@@ -12952,10 +12972,10 @@
     </row>
     <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>920</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>921</v>
       </c>
       <c r="C82" s="7" t="b">
         <v>0</v>
@@ -12969,10 +12989,10 @@
     </row>
     <row r="83" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C83" s="7" t="b">
         <v>0</v>
@@ -12986,10 +13006,10 @@
     </row>
     <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C84" s="7" t="b">
         <v>0</v>
@@ -13003,10 +13023,10 @@
     </row>
     <row r="85" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C85" s="7" t="b">
         <v>0</v>
@@ -13020,10 +13040,10 @@
     </row>
     <row r="86" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C86" s="7" t="b">
         <v>0</v>
@@ -13037,10 +13057,10 @@
     </row>
     <row r="87" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="B87" s="6" t="s">
         <v>889</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>890</v>
       </c>
       <c r="C87" s="7" t="b">
         <v>0</v>
@@ -13054,10 +13074,10 @@
     </row>
     <row r="88" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C88" s="7" t="b">
         <v>0</v>
@@ -13071,10 +13091,10 @@
     </row>
     <row r="89" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C89" s="7" t="b">
         <v>0</v>
@@ -13088,10 +13108,10 @@
     </row>
     <row r="90" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C90" s="7" t="b">
         <v>0</v>
@@ -13105,10 +13125,10 @@
     </row>
     <row r="91" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C91" s="7" t="b">
         <v>0</v>
@@ -13122,10 +13142,10 @@
     </row>
     <row r="92" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C92" s="7" t="b">
         <v>0</v>
@@ -13139,10 +13159,10 @@
     </row>
     <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C93" s="7" t="b">
         <v>0</v>
@@ -13156,10 +13176,10 @@
     </row>
     <row r="94" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C94" s="7" t="b">
         <v>0</v>
@@ -13173,10 +13193,10 @@
     </row>
     <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C95" s="7" t="b">
         <v>0</v>
@@ -13190,10 +13210,10 @@
     </row>
     <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C96" s="7" t="b">
         <v>0</v>
@@ -13207,10 +13227,10 @@
     </row>
     <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C97" s="7" t="b">
         <v>0</v>
@@ -13219,7 +13239,7 @@
         <v>1</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="G97" s="7" t="b">
         <v>0</v>
@@ -13227,10 +13247,10 @@
     </row>
     <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C98" s="7" t="b">
         <v>0</v>
@@ -13239,7 +13259,7 @@
         <v>1</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G98" s="7" t="b">
         <v>0</v>
@@ -13247,10 +13267,10 @@
     </row>
     <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C99" s="7" t="b">
         <v>0</v>
@@ -13264,10 +13284,10 @@
     </row>
     <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C100" s="7" t="b">
         <v>0</v>
@@ -13281,10 +13301,10 @@
     </row>
     <row r="101" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C101" s="7" t="b">
         <v>0</v>
@@ -13298,10 +13318,10 @@
     </row>
     <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C102" s="7" t="b">
         <v>0</v>
@@ -13315,10 +13335,10 @@
     </row>
     <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C103" s="7" t="b">
         <v>0</v>
@@ -13332,10 +13352,10 @@
     </row>
     <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C104" s="7" t="b">
         <v>0</v>
@@ -13349,10 +13369,10 @@
     </row>
     <row r="105" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C105" s="7" t="b">
         <v>0</v>
@@ -13366,10 +13386,10 @@
     </row>
     <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C106" s="7" t="b">
         <v>0</v>
@@ -13383,10 +13403,10 @@
     </row>
     <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C107" s="7" t="b">
         <v>0</v>
@@ -13400,10 +13420,10 @@
     </row>
     <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C108" s="7" t="b">
         <v>0</v>
@@ -13417,10 +13437,10 @@
     </row>
     <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C109" s="7" t="b">
         <v>0</v>
@@ -13434,10 +13454,10 @@
     </row>
     <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C110" s="7" t="b">
         <v>0</v>
@@ -13451,10 +13471,10 @@
     </row>
     <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C111" s="7" t="b">
         <v>0</v>
@@ -13471,7 +13491,7 @@
         <v>316</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C112" s="7" t="b">
         <v>0</v>
@@ -13485,10 +13505,10 @@
     </row>
     <row r="113" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C113" s="7" t="b">
         <v>0</v>
@@ -13502,10 +13522,10 @@
     </row>
     <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C114" s="7" t="b">
         <v>0</v>
@@ -13519,10 +13539,10 @@
     </row>
     <row r="115" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C115" s="7" t="b">
         <v>0</v>
@@ -13536,10 +13556,10 @@
     </row>
     <row r="116" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C116" s="7" t="b">
         <v>0</v>
@@ -13553,10 +13573,10 @@
     </row>
     <row r="117" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="C117" s="7" t="b">
         <v>0</v>
@@ -13613,7 +13633,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -13831,7 +13851,7 @@
         <v>582</v>
       </c>
       <c r="C14" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>594</v>
@@ -14478,7 +14498,7 @@
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>582</v>
@@ -14537,7 +14557,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -15095,7 +15115,7 @@
         <v>502</v>
       </c>
       <c r="C34" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="7" t="b">
         <v>0</v>
@@ -15265,7 +15285,7 @@
         <v>540</v>
       </c>
       <c r="C44" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="7" t="b">
         <v>1</v>
@@ -15421,7 +15441,7 @@
         <v>503</v>
       </c>
       <c r="C53" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="7" t="b">
         <v>1</v>
@@ -15659,7 +15679,7 @@
         <v>505</v>
       </c>
       <c r="C67" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>810</v>
@@ -16259,7 +16279,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -16273,7 +16293,7 @@
         <v>605</v>
       </c>
       <c r="C2" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="7" t="b">
         <v>0</v>
@@ -16290,7 +16310,7 @@
         <v>605</v>
       </c>
       <c r="C3" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="7" t="b">
         <v>1</v>
@@ -16324,7 +16344,7 @@
         <v>605</v>
       </c>
       <c r="C5" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="7" t="b">
         <v>1</v>
@@ -16375,7 +16395,7 @@
         <v>605</v>
       </c>
       <c r="C8" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="7" t="b">
         <v>1</v>
@@ -16596,7 +16616,7 @@
         <v>605</v>
       </c>
       <c r="C21" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="7" t="b">
         <v>1</v>
@@ -16664,7 +16684,7 @@
         <v>605</v>
       </c>
       <c r="C25" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="7" t="b">
         <v>1</v>
@@ -16698,7 +16718,7 @@
         <v>605</v>
       </c>
       <c r="C27" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="7" t="b">
         <v>1</v>
@@ -16715,7 +16735,7 @@
         <v>605</v>
       </c>
       <c r="C28" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="7" t="b">
         <v>1</v>
@@ -16732,7 +16752,7 @@
         <v>605</v>
       </c>
       <c r="C29" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="7" t="b">
         <v>1</v>
@@ -16766,7 +16786,7 @@
         <v>605</v>
       </c>
       <c r="C31" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="7" t="b">
         <v>1</v>
@@ -16953,10 +16973,10 @@
         <v>638</v>
       </c>
       <c r="C42" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" s="7" t="b">
         <v>0</v>
@@ -17004,7 +17024,7 @@
         <v>638</v>
       </c>
       <c r="C45" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="7" t="b">
         <v>1</v>
@@ -17015,7 +17035,7 @@
     </row>
     <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>638</v>
@@ -17030,7 +17050,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -17143,7 +17163,7 @@
         <v>638</v>
       </c>
       <c r="C53" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="7" t="b">
         <v>0</v>
@@ -17177,7 +17197,7 @@
         <v>638</v>
       </c>
       <c r="C55" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="7" t="b">
         <v>1</v>
@@ -17228,7 +17248,7 @@
         <v>638</v>
       </c>
       <c r="C58" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="7" t="b">
         <v>1</v>
@@ -17299,7 +17319,7 @@
         <v>638</v>
       </c>
       <c r="C62" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" s="7" t="b">
         <v>1</v>
@@ -17333,7 +17353,7 @@
         <v>638</v>
       </c>
       <c r="C64" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" s="7" t="b">
         <v>1</v>
@@ -17639,7 +17659,7 @@
         <v>670</v>
       </c>
       <c r="C82" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" s="7" t="b">
         <v>1</v>
@@ -17911,7 +17931,7 @@
         <v>670</v>
       </c>
       <c r="C98" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" s="7" t="b">
         <v>1</v>
@@ -17928,7 +17948,7 @@
         <v>670</v>
       </c>
       <c r="C99" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" s="7" t="b">
         <v>1</v>
@@ -17945,7 +17965,7 @@
         <v>670</v>
       </c>
       <c r="C100" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" s="7" t="b">
         <v>1</v>
@@ -18425,7 +18445,7 @@
         <v>700</v>
       </c>
       <c r="C128" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" s="7" t="b">
         <v>1</v>
@@ -18442,7 +18462,7 @@
         <v>700</v>
       </c>
       <c r="C129" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" s="7" t="b">
         <v>0</v>
@@ -18561,7 +18581,7 @@
         <v>700</v>
       </c>
       <c r="C136" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E136" s="7" t="b">
         <v>1</v>
@@ -18918,7 +18938,7 @@
         <v>768</v>
       </c>
       <c r="C157" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" s="7" t="b">
         <v>1</v>
@@ -18969,7 +18989,7 @@
         <v>768</v>
       </c>
       <c r="C160" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160" s="7" t="b">
         <v>0</v>
@@ -18986,7 +19006,7 @@
         <v>768</v>
       </c>
       <c r="C161" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" s="7" t="b">
         <v>1</v>
@@ -19003,7 +19023,7 @@
         <v>768</v>
       </c>
       <c r="C162" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162" s="7" t="b">
         <v>1</v>
@@ -19031,7 +19051,7 @@
     </row>
     <row r="164" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>638</v>

--- a/ideas_ressources_files/plant_port_checklist.xlsx
+++ b/ideas_ressources_files/plant_port_checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\pvz_zombie_rpg\ideas_ressources_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\- Games\PvZ Game Concept\rogue_garden\ideas_ressources_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F0348A-D41A-445A-A669-5E0AE8230374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11E2328-07F8-4A99-BF26-2DC94715B3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PvZ 1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="956">
   <si>
     <t>Origin Name</t>
   </si>
@@ -2655,6 +2655,9 @@
     <t>Physalux</t>
   </si>
   <si>
+    <t>Acesparagus</t>
+  </si>
+  <si>
     <t>Lime-bomb</t>
   </si>
   <si>
@@ -2898,10 +2901,7 @@
     <t>Shadow Repeater</t>
   </si>
   <si>
-    <t>Aceparagus</t>
-  </si>
-  <si>
-    <t>Squirty-shroom</t>
+    <t>Fire Pea</t>
   </si>
 </sst>
 </file>
@@ -2960,7 +2960,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2995,12 +2995,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3334,7 +3328,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -3348,7 +3342,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="7" t="b">
         <v>0</v>
@@ -3365,7 +3359,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="7" t="b">
         <v>1</v>
@@ -3382,7 +3376,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="7" t="b">
         <v>1</v>
@@ -3399,7 +3393,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="7" t="b">
         <v>1</v>
@@ -3416,7 +3410,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="7" t="b">
         <v>1</v>
@@ -3433,7 +3427,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="7" t="b">
         <v>1</v>
@@ -3450,7 +3444,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="b">
         <v>1</v>
@@ -3467,7 +3461,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7" t="b">
         <v>1</v>
@@ -3484,7 +3478,7 @@
         <v>40</v>
       </c>
       <c r="C10" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="7" t="b">
         <v>0</v>
@@ -3501,7 +3495,7 @@
         <v>40</v>
       </c>
       <c r="C11" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="7" t="b">
         <v>1</v>
@@ -3518,7 +3512,7 @@
         <v>40</v>
       </c>
       <c r="C12" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="b">
         <v>1</v>
@@ -3535,7 +3529,7 @@
         <v>40</v>
       </c>
       <c r="C13" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="7" t="b">
         <v>1</v>
@@ -3552,7 +3546,7 @@
         <v>40</v>
       </c>
       <c r="C14" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="7" t="b">
         <v>1</v>
@@ -3569,7 +3563,7 @@
         <v>40</v>
       </c>
       <c r="C15" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="7" t="b">
         <v>1</v>
@@ -3586,7 +3580,7 @@
         <v>40</v>
       </c>
       <c r="C16" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="7" t="b">
         <v>1</v>
@@ -3603,7 +3597,7 @@
         <v>40</v>
       </c>
       <c r="C17" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="7" t="b">
         <v>1</v>
@@ -3994,7 +3988,7 @@
         <v>22</v>
       </c>
       <c r="C40" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="7" t="b">
         <v>1</v>
@@ -4011,7 +4005,7 @@
         <v>22</v>
       </c>
       <c r="C41" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="7" t="b">
         <v>1</v>
@@ -4028,7 +4022,7 @@
         <v>22</v>
       </c>
       <c r="C42" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="7" t="b">
         <v>0</v>
@@ -4045,7 +4039,7 @@
         <v>22</v>
       </c>
       <c r="C43" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="7" t="b">
         <v>1</v>
@@ -4062,7 +4056,7 @@
         <v>22</v>
       </c>
       <c r="C44" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="7" t="b">
         <v>1</v>
@@ -4079,7 +4073,7 @@
         <v>22</v>
       </c>
       <c r="C45" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="7" t="b">
         <v>1</v>
@@ -4096,7 +4090,7 @@
         <v>22</v>
       </c>
       <c r="C46" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="7" t="b">
         <v>1</v>
@@ -4113,7 +4107,7 @@
         <v>22</v>
       </c>
       <c r="C47" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="7" t="b">
         <v>1</v>
@@ -4198,7 +4192,7 @@
         <v>31</v>
       </c>
       <c r="C52" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="7" t="b">
         <v>1</v>
@@ -4215,7 +4209,7 @@
         <v>31</v>
       </c>
       <c r="C53" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" s="7" t="b">
         <v>1</v>
@@ -4232,7 +4226,7 @@
         <v>31</v>
       </c>
       <c r="C54" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" s="7" t="b">
         <v>1</v>
@@ -4249,7 +4243,7 @@
         <v>31</v>
       </c>
       <c r="C55" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="7" t="b">
         <v>1</v>
@@ -4266,7 +4260,7 @@
         <v>31</v>
       </c>
       <c r="C56" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="7" t="b">
         <v>1</v>
@@ -4283,7 +4277,7 @@
         <v>31</v>
       </c>
       <c r="C57" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="7" t="b">
         <v>1</v>
@@ -4300,7 +4294,7 @@
         <v>31</v>
       </c>
       <c r="C58" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="7" t="b">
         <v>1</v>
@@ -4317,7 +4311,7 @@
         <v>31</v>
       </c>
       <c r="C59" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="7" t="b">
         <v>1</v>
@@ -4334,7 +4328,7 @@
         <v>49</v>
       </c>
       <c r="C60" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="7" t="b">
         <v>1</v>
@@ -4351,7 +4345,7 @@
         <v>49</v>
       </c>
       <c r="C61" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="7" t="b">
         <v>1</v>
@@ -4368,7 +4362,7 @@
         <v>49</v>
       </c>
       <c r="C62" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="7" t="b">
         <v>1</v>
@@ -4385,7 +4379,7 @@
         <v>49</v>
       </c>
       <c r="C63" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" s="7" t="b">
         <v>1</v>
@@ -4402,7 +4396,7 @@
         <v>49</v>
       </c>
       <c r="C64" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" s="7" t="b">
         <v>1</v>
@@ -4436,7 +4430,7 @@
         <v>49</v>
       </c>
       <c r="C66" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="7" t="b">
         <v>1</v>
@@ -4453,7 +4447,7 @@
         <v>49</v>
       </c>
       <c r="C67" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="7" t="b">
         <v>1</v>
@@ -4470,7 +4464,7 @@
         <v>59</v>
       </c>
       <c r="C68" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="7" t="b">
         <v>1</v>
@@ -4487,7 +4481,7 @@
         <v>59</v>
       </c>
       <c r="C69" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" s="7" t="b">
         <v>1</v>
@@ -4504,7 +4498,7 @@
         <v>59</v>
       </c>
       <c r="C70" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="7" t="b">
         <v>1</v>
@@ -4521,7 +4515,7 @@
         <v>59</v>
       </c>
       <c r="C71" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" s="7" t="b">
         <v>1</v>
@@ -4538,7 +4532,7 @@
         <v>59</v>
       </c>
       <c r="C72" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>87</v>
@@ -4558,7 +4552,7 @@
         <v>59</v>
       </c>
       <c r="C73" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" s="7" t="b">
         <v>1</v>
@@ -4575,7 +4569,7 @@
         <v>59</v>
       </c>
       <c r="C74" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="7" t="b">
         <v>1</v>
@@ -4592,7 +4586,7 @@
         <v>59</v>
       </c>
       <c r="C75" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="7" t="b">
         <v>1</v>
@@ -4611,880 +4605,873 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02DA624A-A8AE-417D-8E03-5309B0ED71C8}">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="7.109375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="7.109375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="7.109375" style="8" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="7.109375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:6" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>941</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="E1" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>806</v>
       </c>
-      <c r="B2" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="C2" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>813</v>
       </c>
-      <c r="B3" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="C3" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="B4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="C4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="B5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="C5" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="C6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="E7" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="E8" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="E9" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="E10" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="E11" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="E12" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="E13" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>952</v>
       </c>
-      <c r="B6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>799</v>
-      </c>
-      <c r="B7" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>805</v>
-      </c>
-      <c r="B8" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>801</v>
-      </c>
-      <c r="B9" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>816</v>
-      </c>
-      <c r="B10" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>817</v>
-      </c>
-      <c r="B11" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>818</v>
-      </c>
-      <c r="B12" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>864</v>
-      </c>
-      <c r="B13" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>942</v>
-      </c>
-      <c r="B14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>943</v>
-      </c>
-      <c r="B15" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>944</v>
-      </c>
-      <c r="B16" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>951</v>
-      </c>
-      <c r="B17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" s="7" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>953</v>
-      </c>
-      <c r="B18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" s="7" t="b">
-        <v>1</v>
+      <c r="A18" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>954</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>955</v>
-      </c>
-      <c r="B19" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" s="7" t="b">
+      <c r="A19" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="7" t="b">
+      <c r="A20" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" s="7" t="b">
+      <c r="A21" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" s="7" t="b">
+      <c r="A22" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" s="7" t="b">
+      <c r="A23" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" s="7" t="b">
+      <c r="A24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" s="7" t="b">
+      <c r="A25" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="7" t="b">
+      <c r="A26" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="7" t="b">
+      <c r="A27" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C27" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D28" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" s="7" t="b">
+      <c r="A28" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C28" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" s="7" t="b">
+      <c r="A29" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C29" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D30" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" s="7" t="b">
+      <c r="A30" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C30" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31" s="7" t="b">
+      <c r="A31" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C31" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D32" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D33" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D34" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D35" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F35" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D36" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D38" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D39" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D40" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D41" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D42" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D43" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D44" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F44" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D45" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F45" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D46" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F46" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D47" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D48" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D49" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F49" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D50" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D51" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D52" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D53" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D54" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D55" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D56" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D57" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D58" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F58" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D59" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F59" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D60" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F60" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D61" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D62" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D63" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D64" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F64" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D65" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F65" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D66" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F66" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D67" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F67" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D68" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F68" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D69" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F69" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D70" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F70" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D71" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71" s="7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D72" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F72" s="7" t="b">
+      <c r="A32" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C32" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C33" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C34" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C35" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C36" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C37" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C38" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C39" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C40" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C41" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C42" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C43" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C44" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C45" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C46" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C47" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C48" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C49" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C50" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C51" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C52" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C53" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C54" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C55" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C56" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C57" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C58" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C59" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C60" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C61" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C62" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C63" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C64" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C65" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C66" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C67" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C68" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C69" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C70" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C71" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C72" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" s="7" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:G13">
-    <sortCondition ref="C2:C13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F13">
+    <sortCondition ref="B2:B13"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5526,7 +5513,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -5608,7 +5595,7 @@
         <v>97</v>
       </c>
       <c r="C6" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="7" t="b">
         <v>1</v>
@@ -5727,7 +5714,7 @@
         <v>97</v>
       </c>
       <c r="C13" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="7" t="b">
         <v>0</v>
@@ -5814,7 +5801,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -5828,7 +5815,7 @@
         <v>112</v>
       </c>
       <c r="C2" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="7" t="b">
         <v>0</v>
@@ -5845,7 +5832,7 @@
         <v>113</v>
       </c>
       <c r="C3" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="7" t="b">
         <v>1</v>
@@ -5862,7 +5849,7 @@
         <v>113</v>
       </c>
       <c r="C4" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="7" t="b">
         <v>1</v>
@@ -5879,7 +5866,7 @@
         <v>112</v>
       </c>
       <c r="C5" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="7" t="b">
         <v>0</v>
@@ -5947,7 +5934,7 @@
         <v>113</v>
       </c>
       <c r="C9" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7" t="b">
         <v>1</v>
@@ -6102,7 +6089,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A72B5E-30F7-44EA-9A7D-62AB51A3920C}">
-  <dimension ref="A1:I170"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.77734375" style="5" customWidth="1"/>
@@ -6136,7 +6123,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -6150,7 +6137,7 @@
         <v>126</v>
       </c>
       <c r="C2" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="7" t="b">
         <v>1</v>
@@ -6167,7 +6154,7 @@
         <v>126</v>
       </c>
       <c r="C3" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="7" t="b">
         <v>1</v>
@@ -6201,7 +6188,7 @@
         <v>175</v>
       </c>
       <c r="C5" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="7" t="b">
         <v>1</v>
@@ -6218,7 +6205,7 @@
         <v>175</v>
       </c>
       <c r="C6" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="7" t="b">
         <v>1</v>
@@ -6235,7 +6222,7 @@
         <v>175</v>
       </c>
       <c r="C7" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="7" t="b">
         <v>1</v>
@@ -6252,7 +6239,7 @@
         <v>155</v>
       </c>
       <c r="C8" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="b">
         <v>1</v>
@@ -6286,7 +6273,7 @@
         <v>154</v>
       </c>
       <c r="C10" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="7" t="b">
         <v>0</v>
@@ -6303,7 +6290,7 @@
         <v>154</v>
       </c>
       <c r="C11" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="7" t="b">
         <v>1</v>
@@ -6320,7 +6307,7 @@
         <v>154</v>
       </c>
       <c r="C12" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="b">
         <v>1</v>
@@ -6337,7 +6324,7 @@
         <v>154</v>
       </c>
       <c r="C13" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="7" t="b">
         <v>1</v>
@@ -6371,7 +6358,7 @@
         <v>145</v>
       </c>
       <c r="C15" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="7" t="b">
         <v>1</v>
@@ -6388,7 +6375,7 @@
         <v>145</v>
       </c>
       <c r="C16" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="7" t="b">
         <v>0</v>
@@ -6397,7 +6384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>136</v>
       </c>
@@ -6405,7 +6392,7 @@
         <v>145</v>
       </c>
       <c r="C17" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="7" t="b">
         <v>1</v>
@@ -6414,7 +6401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>139</v>
       </c>
@@ -6422,7 +6409,7 @@
         <v>145</v>
       </c>
       <c r="C18" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="7" t="b">
         <v>1</v>
@@ -6431,7 +6418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>138</v>
       </c>
@@ -6448,7 +6435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>204</v>
       </c>
@@ -6456,7 +6443,7 @@
         <v>205</v>
       </c>
       <c r="C20" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7" t="b">
         <v>1</v>
@@ -6465,7 +6452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>200</v>
       </c>
@@ -6473,16 +6460,22 @@
         <v>205</v>
       </c>
       <c r="C21" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="7" t="b">
         <v>1</v>
       </c>
+      <c r="F21" s="5" t="s">
+        <v>955</v>
+      </c>
       <c r="G21" s="7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H21" s="5" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>196</v>
       </c>
@@ -6490,7 +6483,7 @@
         <v>205</v>
       </c>
       <c r="C22" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="7" t="b">
         <v>1</v>
@@ -6499,7 +6492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>195</v>
       </c>
@@ -6507,7 +6500,7 @@
         <v>205</v>
       </c>
       <c r="C23" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="7" t="b">
         <v>1</v>
@@ -6516,7 +6509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>199</v>
       </c>
@@ -6524,7 +6517,7 @@
         <v>205</v>
       </c>
       <c r="C24" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="7" t="b">
         <v>1</v>
@@ -6533,7 +6526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>203</v>
       </c>
@@ -6550,7 +6543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>201</v>
       </c>
@@ -6558,7 +6551,7 @@
         <v>205</v>
       </c>
       <c r="C26" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7" t="b">
         <v>1</v>
@@ -6567,7 +6560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>194</v>
       </c>
@@ -6575,7 +6568,7 @@
         <v>205</v>
       </c>
       <c r="C27" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="7" t="b">
         <v>1</v>
@@ -6584,7 +6577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>198</v>
       </c>
@@ -6601,7 +6594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>202</v>
       </c>
@@ -6618,7 +6611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>197</v>
       </c>
@@ -6626,7 +6619,7 @@
         <v>205</v>
       </c>
       <c r="C30" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="7" t="b">
         <v>1</v>
@@ -6635,7 +6628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>162</v>
       </c>
@@ -6652,7 +6645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>807</v>
       </c>
@@ -6660,7 +6653,7 @@
         <v>166</v>
       </c>
       <c r="C32" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="7" t="b">
         <v>1</v>
@@ -6677,7 +6670,7 @@
         <v>166</v>
       </c>
       <c r="C33" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="7" t="b">
         <v>1</v>
@@ -6694,7 +6687,7 @@
         <v>166</v>
       </c>
       <c r="C34" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="7" t="b">
         <v>1</v>
@@ -6711,7 +6704,7 @@
         <v>166</v>
       </c>
       <c r="C35" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="7" t="b">
         <v>1</v>
@@ -6728,7 +6721,7 @@
         <v>146</v>
       </c>
       <c r="C36" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="7" t="b">
         <v>1</v>
@@ -6745,7 +6738,7 @@
         <v>146</v>
       </c>
       <c r="C37" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="7" t="b">
         <v>1</v>
@@ -6762,7 +6755,7 @@
         <v>146</v>
       </c>
       <c r="C38" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="7" t="b">
         <v>1</v>
@@ -6796,7 +6789,7 @@
         <v>146</v>
       </c>
       <c r="C40" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="7" t="b">
         <v>1</v>
@@ -6813,7 +6806,7 @@
         <v>176</v>
       </c>
       <c r="C41" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="7" t="b">
         <v>1</v>
@@ -6830,7 +6823,7 @@
         <v>176</v>
       </c>
       <c r="C42" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="7" t="b">
         <v>1</v>
@@ -6847,7 +6840,7 @@
         <v>176</v>
       </c>
       <c r="C43" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="7" t="b">
         <v>1</v>
@@ -6864,7 +6857,7 @@
         <v>176</v>
       </c>
       <c r="C44" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="7" t="b">
         <v>1</v>
@@ -6881,7 +6874,7 @@
         <v>176</v>
       </c>
       <c r="C45" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="7" t="b">
         <v>1</v>
@@ -6898,7 +6891,7 @@
         <v>165</v>
       </c>
       <c r="C46" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="7" t="b">
         <v>1</v>
@@ -6932,7 +6925,7 @@
         <v>165</v>
       </c>
       <c r="C48" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="7" t="b">
         <v>1</v>
@@ -6966,7 +6959,7 @@
         <v>165</v>
       </c>
       <c r="C50" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="7" t="b">
         <v>1</v>
@@ -7003,7 +6996,7 @@
         <v>60</v>
       </c>
       <c r="C52" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="7" t="b">
         <v>0</v>
@@ -7031,7 +7024,7 @@
     </row>
     <row r="54" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>60</v>
@@ -7054,7 +7047,7 @@
         <v>133</v>
       </c>
       <c r="C55" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="7" t="b">
         <v>1</v>
@@ -7071,7 +7064,7 @@
         <v>133</v>
       </c>
       <c r="C56" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="7" t="b">
         <v>1</v>
@@ -7088,7 +7081,7 @@
         <v>133</v>
       </c>
       <c r="C57" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="7" t="b">
         <v>1</v>
@@ -7360,7 +7353,7 @@
         <v>97</v>
       </c>
       <c r="C73" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" s="7" t="b">
         <v>1</v>
@@ -7377,7 +7370,7 @@
         <v>97</v>
       </c>
       <c r="C74" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="7" t="b">
         <v>1</v>
@@ -7394,7 +7387,7 @@
         <v>97</v>
       </c>
       <c r="C75" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="7" t="b">
         <v>1</v>
@@ -7411,7 +7404,7 @@
         <v>97</v>
       </c>
       <c r="C76" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" s="7" t="b">
         <v>1</v>
@@ -7445,7 +7438,7 @@
         <v>97</v>
       </c>
       <c r="C78" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" s="7" t="b">
         <v>1</v>
@@ -7462,7 +7455,7 @@
         <v>97</v>
       </c>
       <c r="C79" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" s="7" t="b">
         <v>1</v>
@@ -7499,7 +7492,7 @@
         <v>97</v>
       </c>
       <c r="C81" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" s="7" t="b">
         <v>1</v>
@@ -7536,7 +7529,7 @@
         <v>97</v>
       </c>
       <c r="C83" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" s="7" t="b">
         <v>1</v>
@@ -7587,7 +7580,7 @@
         <v>97</v>
       </c>
       <c r="C86" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="7" t="b">
         <v>1</v>
@@ -7604,7 +7597,7 @@
         <v>97</v>
       </c>
       <c r="C87" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" s="7" t="b">
         <v>1</v>
@@ -7621,7 +7614,7 @@
         <v>97</v>
       </c>
       <c r="C88" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" s="7" t="b">
         <v>1</v>
@@ -7638,7 +7631,7 @@
         <v>221</v>
       </c>
       <c r="C89" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" s="7" t="b">
         <v>1</v>
@@ -7766,7 +7759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
         <v>224</v>
       </c>
@@ -7783,7 +7776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>253</v>
       </c>
@@ -7799,9 +7792,8 @@
       <c r="G98" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="I98" s="11"/>
-    </row>
-    <row r="99" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
         <v>227</v>
       </c>
@@ -7812,13 +7804,13 @@
         <v>0</v>
       </c>
       <c r="E99" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" s="7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
         <v>259</v>
       </c>
@@ -7835,7 +7827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
         <v>280</v>
       </c>
@@ -7852,7 +7844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>270</v>
       </c>
@@ -7869,7 +7861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>288</v>
       </c>
@@ -7886,7 +7878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>278</v>
       </c>
@@ -7903,7 +7895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>269</v>
       </c>
@@ -7920,8 +7912,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="12" t="s">
+    <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="10" t="s">
         <v>279</v>
       </c>
       <c r="B106" s="6" t="s">
@@ -7937,7 +7929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>300</v>
       </c>
@@ -7954,7 +7946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>287</v>
       </c>
@@ -7971,7 +7963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>222</v>
       </c>
@@ -7979,7 +7971,7 @@
         <v>221</v>
       </c>
       <c r="C109" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" s="7" t="b">
         <v>1</v>
@@ -7991,7 +7983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>242</v>
       </c>
@@ -7999,7 +7991,7 @@
         <v>221</v>
       </c>
       <c r="C110" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" s="7" t="b">
         <v>1</v>
@@ -8008,7 +8000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>235</v>
       </c>
@@ -8025,7 +8017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>257</v>
       </c>
@@ -8084,7 +8076,7 @@
         <v>221</v>
       </c>
       <c r="C115" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" s="7" t="b">
         <v>1</v>
@@ -8101,7 +8093,7 @@
         <v>221</v>
       </c>
       <c r="C116" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" s="7" t="b">
         <v>1</v>
@@ -8152,7 +8144,7 @@
         <v>221</v>
       </c>
       <c r="C119" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" s="7" t="b">
         <v>1</v>
@@ -8288,7 +8280,7 @@
         <v>221</v>
       </c>
       <c r="C127" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E127" s="7" t="b">
         <v>1</v>
@@ -8305,7 +8297,7 @@
         <v>221</v>
       </c>
       <c r="C128" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" s="7" t="b">
         <v>1</v>
@@ -8322,7 +8314,7 @@
         <v>221</v>
       </c>
       <c r="C129" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129" s="7" t="b">
         <v>1</v>
@@ -8356,7 +8348,7 @@
         <v>221</v>
       </c>
       <c r="C131" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131" s="7" t="b">
         <v>0</v>
@@ -8373,7 +8365,7 @@
         <v>221</v>
       </c>
       <c r="C132" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E132" s="7" t="b">
         <v>1</v>
@@ -8492,7 +8484,7 @@
         <v>221</v>
       </c>
       <c r="C139" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E139" s="7" t="b">
         <v>1</v>
@@ -8543,7 +8535,7 @@
         <v>221</v>
       </c>
       <c r="C142" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" s="7" t="b">
         <v>1</v>
@@ -8560,7 +8552,7 @@
         <v>221</v>
       </c>
       <c r="C143" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E143" s="7" t="b">
         <v>0</v>
@@ -8577,7 +8569,7 @@
         <v>221</v>
       </c>
       <c r="C144" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" s="7" t="b">
         <v>1</v>
@@ -8645,7 +8637,7 @@
         <v>221</v>
       </c>
       <c r="C148" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" s="7" t="b">
         <v>1</v>
@@ -8662,7 +8654,7 @@
         <v>221</v>
       </c>
       <c r="C149" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" s="7" t="b">
         <v>1</v>
@@ -8679,7 +8671,7 @@
         <v>221</v>
       </c>
       <c r="C150" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" s="7" t="b">
         <v>1</v>
@@ -8696,7 +8688,7 @@
         <v>221</v>
       </c>
       <c r="C151" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" s="7" t="b">
         <v>1</v>
@@ -8730,7 +8722,7 @@
         <v>221</v>
       </c>
       <c r="C153" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" s="7" t="b">
         <v>0</v>
@@ -8945,7 +8937,7 @@
     </row>
     <row r="166" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>221</v>
@@ -8962,7 +8954,7 @@
     </row>
     <row r="167" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="5" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>221</v>
@@ -8974,7 +8966,7 @@
         <v>1</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="G167" s="7" t="b">
         <v>0</v>
@@ -9005,7 +8997,7 @@
         <v>134</v>
       </c>
       <c r="C169" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E169" s="7" t="b">
         <v>1</v>
@@ -9022,7 +9014,7 @@
         <v>134</v>
       </c>
       <c r="C170" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E170" s="7" t="b">
         <v>1</v>
@@ -9075,7 +9067,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -10169,7 +10161,7 @@
         <v>361</v>
       </c>
       <c r="C65" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="7" t="b">
         <v>1</v>
@@ -10254,7 +10246,7 @@
         <v>361</v>
       </c>
       <c r="C70" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="7" t="b">
         <v>1</v>
@@ -10722,7 +10714,7 @@
         <v>361</v>
       </c>
       <c r="C97" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" s="7" t="b">
         <v>0</v>
@@ -10844,7 +10836,7 @@
         <v>361</v>
       </c>
       <c r="C104" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104" s="7" t="b">
         <v>1</v>
@@ -11159,16 +11151,13 @@
         <v>324</v>
       </c>
       <c r="C122" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>954</v>
+        <v>1</v>
       </c>
       <c r="E122" s="7" t="b">
         <v>1</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>954</v>
+        <v>873</v>
       </c>
       <c r="G122" s="7" t="b">
         <v>0</v>
@@ -11598,7 +11587,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -11626,10 +11615,10 @@
         <v>769</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C3" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="7" t="b">
         <v>0</v>
@@ -11731,7 +11720,7 @@
         <v>782</v>
       </c>
       <c r="C9" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="7" t="b">
         <v>0</v>
@@ -11742,7 +11731,7 @@
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>823</v>
@@ -11799,7 +11788,7 @@
         <v>776</v>
       </c>
       <c r="C13" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="7" t="b">
         <v>1</v>
@@ -11861,7 +11850,7 @@
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>841</v>
@@ -11912,7 +11901,7 @@
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>841</v>
@@ -11952,7 +11941,7 @@
         <v>788</v>
       </c>
       <c r="C22" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="7" t="b">
         <v>0</v>
@@ -11997,7 +11986,7 @@
     </row>
     <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>823</v>
@@ -12167,7 +12156,7 @@
     </row>
     <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>820</v>
@@ -12235,7 +12224,7 @@
     </row>
     <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>841</v>
@@ -12320,7 +12309,7 @@
     </row>
     <row r="44" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>823</v>
@@ -12337,7 +12326,7 @@
     </row>
     <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>841</v>
@@ -12734,7 +12723,7 @@
         <v>556</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C68" s="7" t="b">
         <v>0</v>
@@ -12748,10 +12737,10 @@
     </row>
     <row r="69" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C69" s="7" t="b">
         <v>0</v>
@@ -12765,10 +12754,10 @@
     </row>
     <row r="70" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C70" s="7" t="b">
         <v>0</v>
@@ -12782,10 +12771,10 @@
     </row>
     <row r="71" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C71" s="7" t="b">
         <v>0</v>
@@ -12799,10 +12788,10 @@
     </row>
     <row r="72" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C72" s="7" t="b">
         <v>0</v>
@@ -12816,10 +12805,10 @@
     </row>
     <row r="73" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C73" s="7" t="b">
         <v>0</v>
@@ -12833,10 +12822,10 @@
     </row>
     <row r="74" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C74" s="7" t="b">
         <v>0</v>
@@ -12850,10 +12839,10 @@
     </row>
     <row r="75" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="B75" s="6" t="s">
         <v>908</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>907</v>
       </c>
       <c r="C75" s="7" t="b">
         <v>0</v>
@@ -12867,10 +12856,10 @@
     </row>
     <row r="76" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C76" s="7" t="b">
         <v>0</v>
@@ -12879,7 +12868,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="G76" s="7" t="b">
         <v>0</v>
@@ -12887,10 +12876,10 @@
     </row>
     <row r="77" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C77" s="7" t="b">
         <v>0</v>
@@ -12904,10 +12893,10 @@
     </row>
     <row r="78" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C78" s="7" t="b">
         <v>0</v>
@@ -12921,10 +12910,10 @@
     </row>
     <row r="79" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C79" s="7" t="b">
         <v>0</v>
@@ -12938,10 +12927,10 @@
     </row>
     <row r="80" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C80" s="7" t="b">
         <v>0</v>
@@ -12955,10 +12944,10 @@
     </row>
     <row r="81" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C81" s="7" t="b">
         <v>0</v>
@@ -12972,10 +12961,10 @@
     </row>
     <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C82" s="7" t="b">
         <v>0</v>
@@ -12989,10 +12978,10 @@
     </row>
     <row r="83" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C83" s="7" t="b">
         <v>0</v>
@@ -13006,10 +12995,10 @@
     </row>
     <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="B84" s="6" t="s">
         <v>916</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>915</v>
       </c>
       <c r="C84" s="7" t="b">
         <v>0</v>
@@ -13023,10 +13012,10 @@
     </row>
     <row r="85" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C85" s="7" t="b">
         <v>0</v>
@@ -13040,10 +13029,10 @@
     </row>
     <row r="86" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C86" s="7" t="b">
         <v>0</v>
@@ -13057,10 +13046,10 @@
     </row>
     <row r="87" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C87" s="7" t="b">
         <v>0</v>
@@ -13074,10 +13063,10 @@
     </row>
     <row r="88" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C88" s="7" t="b">
         <v>0</v>
@@ -13091,10 +13080,10 @@
     </row>
     <row r="89" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C89" s="7" t="b">
         <v>0</v>
@@ -13108,10 +13097,10 @@
     </row>
     <row r="90" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C90" s="7" t="b">
         <v>0</v>
@@ -13125,10 +13114,10 @@
     </row>
     <row r="91" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C91" s="7" t="b">
         <v>0</v>
@@ -13142,10 +13131,10 @@
     </row>
     <row r="92" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C92" s="7" t="b">
         <v>0</v>
@@ -13159,10 +13148,10 @@
     </row>
     <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C93" s="7" t="b">
         <v>0</v>
@@ -13176,10 +13165,10 @@
     </row>
     <row r="94" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C94" s="7" t="b">
         <v>0</v>
@@ -13193,10 +13182,10 @@
     </row>
     <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C95" s="7" t="b">
         <v>0</v>
@@ -13210,10 +13199,10 @@
     </row>
     <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C96" s="7" t="b">
         <v>0</v>
@@ -13227,10 +13216,10 @@
     </row>
     <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C97" s="7" t="b">
         <v>0</v>
@@ -13239,7 +13228,7 @@
         <v>1</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="G97" s="7" t="b">
         <v>0</v>
@@ -13247,10 +13236,10 @@
     </row>
     <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C98" s="7" t="b">
         <v>0</v>
@@ -13259,7 +13248,7 @@
         <v>1</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="G98" s="7" t="b">
         <v>0</v>
@@ -13267,10 +13256,10 @@
     </row>
     <row r="99" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C99" s="7" t="b">
         <v>0</v>
@@ -13284,10 +13273,10 @@
     </row>
     <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C100" s="7" t="b">
         <v>0</v>
@@ -13301,10 +13290,10 @@
     </row>
     <row r="101" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C101" s="7" t="b">
         <v>0</v>
@@ -13318,10 +13307,10 @@
     </row>
     <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C102" s="7" t="b">
         <v>0</v>
@@ -13335,10 +13324,10 @@
     </row>
     <row r="103" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C103" s="7" t="b">
         <v>0</v>
@@ -13352,10 +13341,10 @@
     </row>
     <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C104" s="7" t="b">
         <v>0</v>
@@ -13369,10 +13358,10 @@
     </row>
     <row r="105" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C105" s="7" t="b">
         <v>0</v>
@@ -13386,10 +13375,10 @@
     </row>
     <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C106" s="7" t="b">
         <v>0</v>
@@ -13403,10 +13392,10 @@
     </row>
     <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C107" s="7" t="b">
         <v>0</v>
@@ -13420,10 +13409,10 @@
     </row>
     <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C108" s="7" t="b">
         <v>0</v>
@@ -13437,10 +13426,10 @@
     </row>
     <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C109" s="7" t="b">
         <v>0</v>
@@ -13454,10 +13443,10 @@
     </row>
     <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C110" s="7" t="b">
         <v>0</v>
@@ -13471,10 +13460,10 @@
     </row>
     <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C111" s="7" t="b">
         <v>0</v>
@@ -13491,7 +13480,7 @@
         <v>316</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C112" s="7" t="b">
         <v>0</v>
@@ -13505,10 +13494,10 @@
     </row>
     <row r="113" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C113" s="7" t="b">
         <v>0</v>
@@ -13522,10 +13511,10 @@
     </row>
     <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C114" s="7" t="b">
         <v>0</v>
@@ -13539,10 +13528,10 @@
     </row>
     <row r="115" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C115" s="7" t="b">
         <v>0</v>
@@ -13556,10 +13545,10 @@
     </row>
     <row r="116" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C116" s="7" t="b">
         <v>0</v>
@@ -13573,10 +13562,10 @@
     </row>
     <row r="117" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C117" s="7" t="b">
         <v>0</v>
@@ -13633,7 +13622,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -13851,7 +13840,7 @@
         <v>582</v>
       </c>
       <c r="C14" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>594</v>
@@ -14498,7 +14487,7 @@
     </row>
     <row r="52" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>582</v>
@@ -14557,7 +14546,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -15115,7 +15104,7 @@
         <v>502</v>
       </c>
       <c r="C34" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="7" t="b">
         <v>0</v>
@@ -15285,7 +15274,7 @@
         <v>540</v>
       </c>
       <c r="C44" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="7" t="b">
         <v>1</v>
@@ -15441,7 +15430,7 @@
         <v>503</v>
       </c>
       <c r="C53" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" s="7" t="b">
         <v>1</v>
@@ -15679,7 +15668,7 @@
         <v>505</v>
       </c>
       <c r="C67" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>810</v>
@@ -16279,7 +16268,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -16293,7 +16282,7 @@
         <v>605</v>
       </c>
       <c r="C2" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="7" t="b">
         <v>0</v>
@@ -16310,7 +16299,7 @@
         <v>605</v>
       </c>
       <c r="C3" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="7" t="b">
         <v>1</v>
@@ -16344,7 +16333,7 @@
         <v>605</v>
       </c>
       <c r="C5" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="7" t="b">
         <v>1</v>
@@ -16395,7 +16384,7 @@
         <v>605</v>
       </c>
       <c r="C8" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="b">
         <v>1</v>
@@ -16616,7 +16605,7 @@
         <v>605</v>
       </c>
       <c r="C21" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="7" t="b">
         <v>1</v>
@@ -16684,7 +16673,7 @@
         <v>605</v>
       </c>
       <c r="C25" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="7" t="b">
         <v>1</v>
@@ -16718,7 +16707,7 @@
         <v>605</v>
       </c>
       <c r="C27" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="7" t="b">
         <v>1</v>
@@ -16735,7 +16724,7 @@
         <v>605</v>
       </c>
       <c r="C28" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="7" t="b">
         <v>1</v>
@@ -16752,7 +16741,7 @@
         <v>605</v>
       </c>
       <c r="C29" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="7" t="b">
         <v>1</v>
@@ -16786,7 +16775,7 @@
         <v>605</v>
       </c>
       <c r="C31" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="7" t="b">
         <v>1</v>
@@ -16973,10 +16962,10 @@
         <v>638</v>
       </c>
       <c r="C42" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="7" t="b">
         <v>0</v>
@@ -17024,7 +17013,7 @@
         <v>638</v>
       </c>
       <c r="C45" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="7" t="b">
         <v>1</v>
@@ -17035,7 +17024,7 @@
     </row>
     <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>638</v>
@@ -17050,7 +17039,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -17163,7 +17152,7 @@
         <v>638</v>
       </c>
       <c r="C53" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" s="7" t="b">
         <v>0</v>
@@ -17197,7 +17186,7 @@
         <v>638</v>
       </c>
       <c r="C55" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="7" t="b">
         <v>1</v>
@@ -17248,7 +17237,7 @@
         <v>638</v>
       </c>
       <c r="C58" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="7" t="b">
         <v>1</v>
@@ -17319,7 +17308,7 @@
         <v>638</v>
       </c>
       <c r="C62" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="7" t="b">
         <v>1</v>
@@ -17353,7 +17342,7 @@
         <v>638</v>
       </c>
       <c r="C64" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" s="7" t="b">
         <v>1</v>
@@ -17659,7 +17648,7 @@
         <v>670</v>
       </c>
       <c r="C82" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" s="7" t="b">
         <v>1</v>
@@ -17931,7 +17920,7 @@
         <v>670</v>
       </c>
       <c r="C98" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" s="7" t="b">
         <v>1</v>
@@ -17948,7 +17937,7 @@
         <v>670</v>
       </c>
       <c r="C99" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" s="7" t="b">
         <v>1</v>
@@ -17965,7 +17954,7 @@
         <v>670</v>
       </c>
       <c r="C100" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" s="7" t="b">
         <v>1</v>
@@ -18445,7 +18434,7 @@
         <v>700</v>
       </c>
       <c r="C128" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" s="7" t="b">
         <v>1</v>
@@ -18462,7 +18451,7 @@
         <v>700</v>
       </c>
       <c r="C129" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129" s="7" t="b">
         <v>0</v>
@@ -18581,7 +18570,7 @@
         <v>700</v>
       </c>
       <c r="C136" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136" s="7" t="b">
         <v>1</v>
@@ -18938,7 +18927,7 @@
         <v>768</v>
       </c>
       <c r="C157" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" s="7" t="b">
         <v>1</v>
@@ -18989,7 +18978,7 @@
         <v>768</v>
       </c>
       <c r="C160" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E160" s="7" t="b">
         <v>0</v>
@@ -19006,7 +18995,7 @@
         <v>768</v>
       </c>
       <c r="C161" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" s="7" t="b">
         <v>1</v>
@@ -19023,7 +19012,7 @@
         <v>768</v>
       </c>
       <c r="C162" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E162" s="7" t="b">
         <v>1</v>
@@ -19051,7 +19040,7 @@
     </row>
     <row r="164" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>638</v>
